--- a/public/exports-from-60-with-coowners/29189129.xlsx
+++ b/public/exports-from-60-with-coowners/29189129.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -18889,7 +18889,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558062</t>
+          <t xml:space="preserve">311558064</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189129.xlsx
+++ b/public/exports-from-60-with-coowners/29189129.xlsx
@@ -18889,7 +18889,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558064</t>
+          <t xml:space="preserve">311558062</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922583</t>
+          <t xml:space="preserve">311926361</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-17</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
